--- a/defect report fh.xlsx
+++ b/defect report fh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c7dd620d9e945120/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{725B3AE7-FDD0-4CC5-8420-0609ABA4D813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{725B3AE7-FDD0-4CC5-8420-0609ABA4D813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54A6C798-1B09-46A4-8A1A-DB951A06B90A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{78C36448-60CE-4523-BEBB-50CE019C3EEF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="64">
   <si>
     <t>defect id</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>https://prnt.sc/BdmXaSSimkpH</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -626,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1581E1-2604-44AD-9E86-F493BC346013}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -1044,6 +1047,11 @@
       </c>
       <c r="I14" s="3" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F15" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
